--- a/OUTPUT/RealizeReports/Manzarul.xlsx
+++ b/OUTPUT/RealizeReports/Manzarul.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Manzarul" displayName="Manzarul" ref="A1:Y6" headerRowCount="1">
-  <autoFilter ref="A1:Y6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Manzarul" displayName="Manzarul" ref="A1:Y25" headerRowCount="1">
+  <autoFilter ref="A1:Y25"/>
   <tableColumns count="25">
     <tableColumn id="1" name="SL"/>
     <tableColumn id="2" name="LC_Factory"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>43676</v>
+        <v>13167</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11251</v>
+        <v>11704</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9201</v>
+        <v>18051</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32312</v>
+        <v>22186</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -909,22 +909,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HONGKONG CH COMPANY LIMITED</t>
+          <t>LOJAS RENNER</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2608888</t>
+          <t>2608294</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46236</v>
+        <v>46225</v>
       </c>
       <c r="G5" t="n">
-        <v>5277</v>
+        <v>5487</v>
       </c>
       <c r="H5" t="n">
-        <v>8812.59</v>
+        <v>26447.34</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5277</v>
+        <v>5487</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46249.82021990741</v>
+        <v>46261.76817129629</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46259</v>
+        <v>46273</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -953,21 +953,21 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t xml:space="preserve">Al Arafah </t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8812.59</t>
+          <t>26447.34</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>46279</v>
+        <v>46292</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30720</v>
+        <v>1857</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HAGGAR CLOTHING CO.</t>
+          <t>NEXT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2608929</t>
+          <t>2608293</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="G6" t="n">
-        <v>6621</v>
+        <v>1459</v>
       </c>
       <c r="H6" t="n">
-        <v>35356.14</v>
+        <v>27519.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6621</v>
+        <v>1459</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46238.77584490741</v>
+        <v>46226</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1048,21 +1048,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t xml:space="preserve">Al Arafah </t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>35356.14</t>
+          <t>27519.50</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1078,6 +1078,1811 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>40222</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Best Seller</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2608685</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H7" t="n">
+        <v>627</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>46231.59276620371</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M7" t="n">
+        <v>33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>74883.75</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14831</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Best Seller</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2608700</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G8" t="n">
+        <v>75</v>
+      </c>
+      <c r="H8" t="n">
+        <v>293.55</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>75</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>46232.49043981481</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>74883.75</t>
+        </is>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6687</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2608696</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G9" t="n">
+        <v>986</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4583.15</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>986</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>46232.71216435185</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="M9" t="n">
+        <v>190.96</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jabel-Ali</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>40978.25</t>
+        </is>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3958</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2608802</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2261</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7999.96</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2261</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46235.45158564814</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="M10" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>40978.25</t>
+        </is>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16062</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2609000</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4200</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14462.4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="M11" t="n">
+        <v>602.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>40978.25</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>37486</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2609044</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1062</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4716.07</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1062</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46242.63420138889</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="M12" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jabel-Ali</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>40978.25</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>28699</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2609045</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2254</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9216.67</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2254</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46242.63420138889</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="M13" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jabel-Ali</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>40978.25</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13435</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2609053</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4829</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18833.1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>4829</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46261.76322916667</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>35519</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2609161</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1004</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9799.040000000001</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1004</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>46253.76475694445</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15943</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2609271</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6014</v>
+      </c>
+      <c r="H16" t="n">
+        <v>49856.06</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6014</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>46260.80262731481</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2299</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Best Seller</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2609401</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4845</v>
+      </c>
+      <c r="H17" t="n">
+        <v>29457.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4845</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46257.54137731482</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1550.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sea/Air</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>74883.75</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>580</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2609399</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5978</v>
+      </c>
+      <c r="H18" t="n">
+        <v>27498.8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5978</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46260.80262731481</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>29666</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Best Seller</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2609402</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7320</v>
+      </c>
+      <c r="H19" t="n">
+        <v>44505.6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>7320</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46257.54137731482</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2342.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sea/Air</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>74883.75</t>
+        </is>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>40184</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2609414</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6907</v>
+      </c>
+      <c r="H20" t="n">
+        <v>26108.46</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6907</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>46263.37321759259</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15227</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2609443</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4955</v>
+      </c>
+      <c r="H21" t="n">
+        <v>18729.9</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>4955</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>46263.37321759259</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17345</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2609465</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3583</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12003.05</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3583</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>46260.80166666667</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18997</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2609464</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3004</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9702.92</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3004</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46263.37321759259</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1448</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LOJAS RENNER</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2609738</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11108.24</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1144</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>46266.79041666666</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>183.63957</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>28654</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Best Seller</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2609762</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16159.5</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>46260.60792824074</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="M25" t="n">
+        <v>850.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Arafah </t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>FDBC-974/26</t>
+        </is>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/OUTPUT/RealizeReports/Manzarul.xlsx
+++ b/OUTPUT/RealizeReports/Manzarul.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Manzarul" displayName="Manzarul" ref="A1:Y25" headerRowCount="1">
-  <autoFilter ref="A1:Y25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Manzarul" displayName="Manzarul" ref="A1:Y24" headerRowCount="1">
+  <autoFilter ref="A1:Y24"/>
   <tableColumns count="25">
     <tableColumn id="1" name="SL"/>
     <tableColumn id="2" name="LC_Factory"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13167</v>
+        <v>14097</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11704</v>
+        <v>37522</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18051</v>
+        <v>2407</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22186</v>
+        <v>20262</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2608294</t>
+          <t>2606659</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="G5" t="n">
-        <v>5487</v>
+        <v>1999</v>
       </c>
       <c r="H5" t="n">
-        <v>26447.34</v>
+        <v>7376.31</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5487</v>
+        <v>1999</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46261.76817129629</v>
+        <v>46263.37321759259</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>26447.34</t>
+          <t>45795.33</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1857</v>
+        <v>40344</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>Primark</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2608293</t>
+          <t>2606662</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="G6" t="n">
-        <v>1459</v>
+        <v>20000</v>
       </c>
       <c r="H6" t="n">
-        <v>27519.5</v>
+        <v>66000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1459</v>
+        <v>20000</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46226</v>
+        <v>46188.76013888889</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46238</v>
+        <v>46196</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1048,21 +1048,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Felixtowe</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Arafah </t>
+          <t>ABL</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>27519.50</t>
+          <t>US$66,000.00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>40222</v>
+        <v>12329</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>LOJAS RENNER</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2608685</t>
+          <t>2606658</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46231</v>
+        <v>46188</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>2476</v>
       </c>
       <c r="H7" t="n">
-        <v>627</v>
+        <v>9136.440000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>120</v>
+        <v>2476</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46231.59276620371</v>
+        <v>46268.69798611111</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="M7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1153,11 +1153,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>74883.75</t>
+          <t>43133.46</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14831</v>
+        <v>40731</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>LOJAS RENNER</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2608700</t>
+          <t>2608294</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>5487</v>
       </c>
       <c r="H8" t="n">
-        <v>293.55</v>
+        <v>26447.34</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1217,16 +1217,16 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>75</v>
+        <v>5487</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46232.49043981481</v>
+        <v>46261.76817129629</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46265</v>
+        <v>46273</v>
       </c>
       <c r="M8" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>74883.75</t>
+          <t>26447.34</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6687</v>
+        <v>2802</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1289,22 +1289,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2608696</t>
+          <t>2608304</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="G9" t="n">
-        <v>986</v>
+        <v>1815</v>
       </c>
       <c r="H9" t="n">
-        <v>4583.15</v>
+        <v>9870.969999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>986</v>
+        <v>1815</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46232.71216435185</v>
+        <v>46259.79888888889</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46251</v>
+        <v>46268</v>
       </c>
       <c r="M9" t="n">
-        <v>190.96</v>
+        <v>519.53</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1333,21 +1333,21 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jabel-Ali</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t xml:space="preserve">Al Arafah </t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>40978.25</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3958</v>
+        <v>1142</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1384,22 +1384,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>Geniemode Bd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2608802</t>
+          <t>2608942</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="G10" t="n">
-        <v>2261</v>
+        <v>720</v>
       </c>
       <c r="H10" t="n">
-        <v>7999.96</v>
+        <v>2772</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2261</v>
+        <v>720</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46235.45158564814</v>
+        <v>46238</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="M10" t="n">
-        <v>333.33</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1438,11 +1438,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>40978.25</t>
+          <t>4620.00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>46287</v>
+        <v>46296</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16062</v>
+        <v>23731</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1479,39 +1479,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>Geniemode Bd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2609000</t>
+          <t>2608943</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G11" t="n">
+        <v>480</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1848</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>480</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="G11" t="n">
-        <v>4200</v>
-      </c>
-      <c r="H11" t="n">
-        <v>14462.4</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MGNSL</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>4200</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>46239</v>
-      </c>
       <c r="L11" s="1" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="M11" t="n">
-        <v>602.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1533,11 +1533,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>40978.25</t>
+          <t>4620.00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>46287</v>
+        <v>46296</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37486</v>
+        <v>18240</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1574,22 +1574,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>LOJAS RENNER</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2609044</t>
+          <t>2609670</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="G12" t="n">
-        <v>1062</v>
+        <v>4925</v>
       </c>
       <c r="H12" t="n">
-        <v>4716.07</v>
+        <v>18173.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1062</v>
+        <v>4925</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46242.63420138889</v>
+        <v>46267.69519675926</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46248</v>
+        <v>46279</v>
       </c>
       <c r="M12" t="n">
-        <v>196.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jabel-Ali</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t xml:space="preserve">Al Arafah </t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>40978.25</t>
+          <t>43133.46</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>46287</v>
+        <v>46296</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28699</v>
+        <v>25175</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1669,22 +1669,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2609045</t>
+          <t>2609755</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46242</v>
+        <v>46259</v>
       </c>
       <c r="G13" t="n">
-        <v>2254</v>
+        <v>2538</v>
       </c>
       <c r="H13" t="n">
-        <v>9216.67</v>
+        <v>12701.88</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2254</v>
+        <v>2538</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46242.63420138889</v>
+        <v>46259.79888888889</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46248</v>
+        <v>46268</v>
       </c>
       <c r="M13" t="n">
-        <v>384.03</v>
+        <v>668.52</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1713,21 +1713,21 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jabel-Ali</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t xml:space="preserve">Al Arafah </t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>40978.25</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13435</v>
+        <v>1179</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1764,22 +1764,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LOJAS RENNER</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2609053</t>
+          <t>2609746</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46243</v>
+        <v>46259</v>
       </c>
       <c r="G14" t="n">
-        <v>4829</v>
+        <v>84</v>
       </c>
       <c r="H14" t="n">
-        <v>18833.1</v>
+        <v>542.64</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1787,16 +1787,16 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4829</v>
+        <v>84</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46261.76322916667</v>
+        <v>46260</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>28.56</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>35519</v>
+        <v>33237</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1864,17 +1864,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2609161</t>
+          <t>2609865</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46246</v>
+        <v>46261</v>
       </c>
       <c r="G15" t="n">
-        <v>1004</v>
+        <v>3198</v>
       </c>
       <c r="H15" t="n">
-        <v>9799.040000000001</v>
+        <v>10329.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1004</v>
+        <v>3198</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46253.76475694445</v>
+        <v>46268.69798611111</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>43133.46</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15943</v>
+        <v>22061</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1959,17 +1959,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2609271</t>
+          <t>2609864</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="G16" t="n">
-        <v>6014</v>
+        <v>6998</v>
       </c>
       <c r="H16" t="n">
-        <v>49856.06</v>
+        <v>38419.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6014</v>
+        <v>6998</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46260.80262731481</v>
+        <v>46267.6990162037</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2008,11 +2008,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>45795.33</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2299</v>
+        <v>20419</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2049,22 +2049,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>LOJAS RENNER</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2609401</t>
+          <t>2609874</t>
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>46250</v>
+        <v>46264</v>
       </c>
       <c r="G17" t="n">
-        <v>4845</v>
+        <v>1701</v>
       </c>
       <c r="H17" t="n">
-        <v>29457.6</v>
+        <v>5494.23</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2072,28 +2072,28 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4845</v>
+        <v>1701</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46257.54137731482</v>
+        <v>46268.69798611111</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="M17" t="n">
-        <v>1550.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sea/Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>74883.75</t>
+          <t>43133.46</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>580</v>
+        <v>21387</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2149,17 +2149,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2609399</t>
+          <t>2609991</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46250</v>
+        <v>46265</v>
       </c>
       <c r="G18" t="n">
-        <v>5978</v>
+        <v>1869</v>
       </c>
       <c r="H18" t="n">
-        <v>27498.8</v>
+        <v>7718.97</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5978</v>
+        <v>1869</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46260.80262731481</v>
+        <v>46268.69798611111</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>7718.97</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>29666</v>
+        <v>39294</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2244,17 +2244,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2609402</t>
+          <t>2610007</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>46250</v>
+        <v>46266</v>
       </c>
       <c r="G19" t="n">
-        <v>7320</v>
+        <v>1422</v>
       </c>
       <c r="H19" t="n">
-        <v>44505.6</v>
+        <v>9591.389999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2262,28 +2262,28 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7320</v>
+        <v>1422</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46257.54137731482</v>
+        <v>46268</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46262</v>
+        <v>46275</v>
       </c>
       <c r="M19" t="n">
-        <v>2342.4</v>
+        <v>504.81</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sea/Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2293,11 +2293,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>74883.75</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40184</v>
+        <v>24110</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2334,22 +2334,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LOJAS RENNER</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2609414</t>
+          <t>2609995</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="G20" t="n">
-        <v>6907</v>
+        <v>1260</v>
       </c>
       <c r="H20" t="n">
-        <v>26108.46</v>
+        <v>8498.700000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2357,16 +2357,16 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6907</v>
+        <v>1260</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46263.37321759259</v>
+        <v>46267</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>447.3</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15227</v>
+        <v>40031</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2429,22 +2429,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LOJAS RENNER</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2609443</t>
+          <t>2610006</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>46252</v>
+        <v>46266</v>
       </c>
       <c r="G21" t="n">
-        <v>4955</v>
+        <v>1626</v>
       </c>
       <c r="H21" t="n">
-        <v>18729.9</v>
+        <v>10246.89</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2452,16 +2452,16 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4955</v>
+        <v>1626</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46263.37321759259</v>
+        <v>46268</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>539.3099999999999</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2483,11 +2483,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17345</v>
+        <v>5730</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2524,22 +2524,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LOJAS RENNER</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2609465</t>
+          <t>2610020</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>46253</v>
+        <v>46267</v>
       </c>
       <c r="G22" t="n">
-        <v>3583</v>
+        <v>1080</v>
       </c>
       <c r="H22" t="n">
-        <v>12003.05</v>
+        <v>5643</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3583</v>
+        <v>1080</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46260.80166666667</v>
+        <v>46268</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2578,11 +2578,11 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>18997</v>
+        <v>11027</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2619,22 +2619,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LOJAS RENNER</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2609464</t>
+          <t>2610117</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>46253</v>
+        <v>46271</v>
       </c>
       <c r="G23" t="n">
-        <v>3004</v>
+        <v>300</v>
       </c>
       <c r="H23" t="n">
-        <v>9702.92</v>
+        <v>1667.25</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2642,28 +2642,28 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3004</v>
+        <v>300</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46263.37321759259</v>
+        <v>46270.59667824074</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>87.75</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Sea/Air</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1448</v>
+        <v>23012</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2714,22 +2714,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LOJAS RENNER</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2609738</t>
+          <t>2610118</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>46258</v>
+        <v>46271</v>
       </c>
       <c r="G24" t="n">
-        <v>1144</v>
+        <v>300</v>
       </c>
       <c r="H24" t="n">
-        <v>11108.24</v>
+        <v>1667.25</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2737,28 +2737,28 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1144</v>
+        <v>300</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46266.79041666666</v>
+        <v>46270.59667824074</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>87.75</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Sea/Air</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>183.63957</t>
+          <t>60429.97</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2788,101 +2788,6 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>28654</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MGNSL</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Woven</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Best Seller</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2609762</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H25" t="n">
-        <v>16159.5</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>MGNSL</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <v>46260.60792824074</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="M25" t="n">
-        <v>850.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Sea</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al Arafah </t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>FDBC-974/26</t>
-        </is>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Realize Pending</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
